--- a/data/trans_dic/P32C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,66</t>
+          <t>0,21; 1,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,87</t>
+          <t>0,57; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,65</t>
+          <t>0,85; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,66</t>
+          <t>0,17; 1,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,22</t>
+          <t>0,15; 1,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,24</t>
+          <t>0,5; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,61</t>
+          <t>0,53; 2,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,57</t>
+          <t>0,3; 1,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,88</t>
+          <t>0,69; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,71</t>
+          <t>0,67; 2,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,94</t>
+          <t>0,69; 2,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,99</t>
+          <t>0,75; 3,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,17</t>
+          <t>0,49; 4,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,97</t>
+          <t>0,46; 2,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,85</t>
+          <t>0,42; 1,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,07</t>
+          <t>0,52; 2,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,79</t>
+          <t>0,9; 2,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,73</t>
+          <t>1,66; 5,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,78</t>
+          <t>1,14; 4,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,66</t>
+          <t>0,91; 3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,41</t>
+          <t>1,31; 4,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,82</t>
+          <t>0,78; 2,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,53</t>
+          <t>0,6; 2,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,14</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,02</t>
+          <t>1,27; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,89</t>
+          <t>1,69; 4,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,43</t>
+          <t>0,53; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,01</t>
+          <t>0,79; 3,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,38</t>
+          <t>1,01; 5,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,58</t>
+          <t>0,49; 2,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,88</t>
+          <t>0,28; 1,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,68</t>
+          <t>1,66; 3,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,24</t>
+          <t>1,19; 3,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,21</t>
+          <t>0,71; 2,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,12</t>
+          <t>0,66; 2,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,65</t>
+          <t>1,34; 2,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,8</t>
+          <t>1,43; 2,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,25</t>
+          <t>1,11; 2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,74</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,83</t>
+          <t>0,39; 1,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,19; 1,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,83</t>
+          <t>0,33; 1,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,15</t>
+          <t>1,14; 2,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,94</t>
+          <t>1,02; 1,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,67</t>
+          <t>0,88; 1,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,55</t>
+          <t>0,71; 1,53</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>898; 7271</t>
+          <t>905; 7581</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2849; 12198</t>
+          <t>2433; 12256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3230; 15433</t>
+          <t>3579; 16005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>577; 5537</t>
+          <t>571; 5994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5026</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1838</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>904; 7542</t>
+          <t>904; 7870</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3215; 13369</t>
+          <t>3013; 13655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3085; 15818</t>
+          <t>3197; 15387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1441; 7727</t>
+          <t>1488; 8529</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3943; 16747</t>
+          <t>4005; 17575</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4038; 16034</t>
+          <t>3948; 16534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4180; 16617</t>
+          <t>3929; 16767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3405; 14274</t>
+          <t>3579; 14850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2094</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 5558</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>987; 10429</t>
+          <t>978; 9710</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3686; 16929</t>
+          <t>3996; 17309</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4084; 16376</t>
+          <t>3732; 15973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4629; 18239</t>
+          <t>4604; 18153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5468; 18915</t>
+          <t>6119; 20050</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5552; 18912</t>
+          <t>5478; 19140</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5088; 17349</t>
+          <t>5227; 18389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3781; 15617</t>
+          <t>3868; 16208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7923</t>
+          <t>0; 8344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1838</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2172</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 14080</t>
+          <t>0; 14747</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5814; 20247</t>
+          <t>6021; 21540</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5063; 18735</t>
+          <t>5149; 19009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4013; 16553</t>
+          <t>3949; 15556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>845; 15036</t>
+          <t>0; 14121</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6802; 21277</t>
+          <t>6716; 21210</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9246; 27258</t>
+          <t>9426; 27406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2939; 13739</t>
+          <t>3000; 13748</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3220; 13359</t>
+          <t>3489; 13430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3947; 16409</t>
+          <t>3090; 16403</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6143</t>
+          <t>0; 6879</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1957; 10394</t>
+          <t>1990; 12040</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>784; 5447</t>
+          <t>803; 5487</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12504; 30704</t>
+          <t>13852; 31592</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11236; 30028</t>
+          <t>10993; 29373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6317; 21399</t>
+          <t>6871; 20934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5041; 15577</t>
+          <t>4808; 14654</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24534; 49733</t>
+          <t>25161; 49639</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29656; 56954</t>
+          <t>29063; 54709</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22488; 44608</t>
+          <t>22072; 45121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11182; 27422</t>
+          <t>12648; 27601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3529; 16377</t>
+          <t>3470; 17009</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1001; 9173</t>
+          <t>997; 8400</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2921; 13756</t>
+          <t>2095; 12883</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3608; 18783</t>
+          <t>3393; 18061</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31280; 59731</t>
+          <t>31509; 57626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31615; 59712</t>
+          <t>31268; 59237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27679; 52044</t>
+          <t>27460; 51938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19245; 40527</t>
+          <t>18427; 39892</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Habitat-trans_dic.xlsx
@@ -664,47 +664,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,73</t>
+          <t>0,21; 1,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,88</t>
+          <t>0,56; 2,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,79</t>
+          <t>0,79; 3,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,27</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,29</t>
+          <t>0,54; 2,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,54</t>
+          <t>0,52; 2,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,73</t>
+          <t>0,27; 1,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,02</t>
+          <t>0,7; 3,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,8</t>
+          <t>0,68; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,96</t>
+          <t>0,57; 2,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,11</t>
+          <t>0,61; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,82</t>
+          <t>0,46; 4,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,01</t>
+          <t>0,43; 2,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,81</t>
+          <t>0,45; 1,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,06</t>
+          <t>0,53; 1,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,96</t>
+          <t>0,88; 2,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,8</t>
+          <t>1,82; 6,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,01</t>
+          <t>1,11; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,8</t>
+          <t>0,91; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,69</t>
+          <t>1,25; 4,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,86</t>
+          <t>0,8; 2,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,37</t>
+          <t>0,6; 2,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,2; 2,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,01</t>
+          <t>1,3; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,92</t>
+          <t>1,75; 4,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,43</t>
+          <t>0,53; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,03</t>
+          <t>0,73; 2,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,38</t>
+          <t>1,01; 5,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,99</t>
+          <t>0,49; 2,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,89</t>
+          <t>0,39; 4,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,79</t>
+          <t>1,54; 3,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,17</t>
+          <t>1,18; 3,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,16</t>
+          <t>0,63; 2,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,0</t>
+          <t>0,87; 2,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,64</t>
+          <t>1,3; 2,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,69</t>
+          <t>1,5; 2,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,28</t>
+          <t>1,12; 2,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>0,1; 0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,19; 1,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,76</t>
+          <t>0,56; 2,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,08</t>
+          <t>1,13; 2,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,93</t>
+          <t>1,04; 1,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,67</t>
+          <t>0,86; 1,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,53</t>
+          <t>0,85; 1,76</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3756</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>905; 7581</t>
+          <t>902; 7408</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2433; 12256</t>
+          <t>2373; 11223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3579; 16005</t>
+          <t>3319; 16522</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>571; 5994</t>
+          <t>556; 5984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 5558</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1680,27 +1680,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>904; 7870</t>
+          <t>901; 8328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3013; 13655</t>
+          <t>3207; 13107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3197; 15387</t>
+          <t>3133; 16886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1488; 8529</t>
+          <t>1427; 8038</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10911</t>
         </is>
       </c>
     </row>
@@ -1853,22 +1853,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4005; 17575</t>
+          <t>4050; 18352</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3948; 16534</t>
+          <t>4025; 15958</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3929; 16767</t>
+          <t>3217; 15772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3579; 14850</t>
+          <t>3048; 13281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1883,32 +1883,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5558</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>978; 9710</t>
+          <t>1020; 9486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3996; 17309</t>
+          <t>3724; 17598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3732; 15973</t>
+          <t>4012; 16052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4604; 18153</t>
+          <t>4663; 17181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6119; 20050</t>
+          <t>6355; 19498</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4526</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5478; 19140</t>
+          <t>6010; 20976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5227; 18389</t>
+          <t>5084; 17861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3868; 16208</t>
+          <t>3868; 16312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8344</t>
+          <t>0; 7951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 14747</t>
+          <t>0; 10926</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6021; 21540</t>
+          <t>5758; 19292</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5149; 19009</t>
+          <t>5283; 19033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3949; 15556</t>
+          <t>3929; 15230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 14121</t>
+          <t>1142; 14752</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>12308</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6716; 21210</t>
+          <t>6883; 21347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9426; 27406</t>
+          <t>9742; 26168</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3000; 13748</t>
+          <t>2987; 14112</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3489; 13430</t>
+          <t>3410; 13810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3090; 16403</t>
+          <t>3070; 16760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6879</t>
+          <t>0; 6317</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1990; 12040</t>
+          <t>1985; 11435</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>803; 5487</t>
+          <t>1204; 14250</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13852; 31592</t>
+          <t>12819; 32751</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10993; 29373</t>
+          <t>10929; 29996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6871; 20934</t>
+          <t>6111; 20336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4808; 14654</t>
+          <t>6721; 22560</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>31502</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25161; 49639</t>
+          <t>24416; 48743</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29063; 54709</t>
+          <t>30521; 56367</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22072; 45121</t>
+          <t>22204; 44470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12648; 27601</t>
+          <t>13181; 29087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3470; 17009</t>
+          <t>3702; 16168</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>997; 8400</t>
+          <t>992; 8150</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2095; 12883</t>
+          <t>2095; 12297</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3393; 18061</t>
+          <t>5046; 23533</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31509; 57626</t>
+          <t>31482; 57897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31268; 59237</t>
+          <t>31979; 58695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27460; 51938</t>
+          <t>26676; 51967</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18427; 39892</t>
+          <t>21866; 45461</t>
         </is>
       </c>
     </row>
